--- a/EKG_Kalite_Yönetim_Sistemi/01_Kurumsal Yönetim - Tesis/03_CMP3 - Tedarikçi ve Dış Kaynak Yönetimi/EKG-STN-FRM-08_dis_kaynak_toz_boya_sevkdonus_lot_eslestirme_ve_kabul_k.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/01_Kurumsal Yönetim - Tesis/03_CMP3 - Tedarikçi ve Dış Kaynak Yönetimi/EKG-STN-FRM-08_dis_kaynak_toz_boya_sevkdonus_lot_eslestirme_ve_kabul_k.xlsx
@@ -1097,7 +1097,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-STN-FRM-08&amp;C&amp;"Arial,Regular"&amp;11Dış Kaynak Toz Boya Sevk-Dönüş, Lot Eşleştirme ve Kabul Kontrol Kaydı</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 08.06.2026 | Revizyon: 16.09.2026
+Revizyon nedeni: Sevk/dönüş ve lot kontrolü korundu; miktar farkı hesabı negatif/eksik girdide sonuç üretmeyecek şekilde düzeltildi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R035156a26aba43e8"/>
   <x:tableParts count="1">
@@ -1414,7 +1415,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-STN-FRM-08&amp;C&amp;"Arial,Regular"&amp;11Dış Kaynak Toz Boya Sevk-Dönüş, Lot Eşleştirme ve Kabul Kontrol Kaydı</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 08.06.2026 | Revizyon: 16.09.2026
+Revizyon nedeni: Sevk/dönüş ve lot kontrolü korundu; miktar farkı hesabı negatif/eksik girdide sonuç üretmeyecek şekilde düzeltildi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3f4aa991d5a043af"/>
   <x:tableParts count="1">
@@ -1765,7 +1767,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-STN-FRM-08&amp;C&amp;"Arial,Regular"&amp;11Dış Kaynak Toz Boya Sevk-Dönüş, Lot Eşleştirme ve Kabul Kontrol Kaydı</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 08.06.2026 | Revizyon: 16.09.2026
+Revizyon nedeni: Sevk/dönüş ve lot kontrolü korundu; miktar farkı hesabı negatif/eksik girdide sonuç üretmeyecek şekilde düzeltildi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R47149d8d0d224d73"/>
   <x:tableParts count="1">
@@ -2117,7 +2120,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-STN-FRM-08&amp;C&amp;"Arial,Regular"&amp;11Dış Kaynak Toz Boya Sevk-Dönüş, Lot Eşleştirme ve Kabul Kontrol Kaydı</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 08.06.2026 | Revizyon: 16.09.2026
+Revizyon nedeni: Sevk/dönüş ve lot kontrolü korundu; miktar farkı hesabı negatif/eksik girdide sonuç üretmeyecek şekilde düzeltildi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1b2b79883fa54e19"/>
   <x:tableParts count="1">
